--- a/BiweeklyResourceData.xlsx
+++ b/BiweeklyResourceData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21f9a9817e5ffdc2/Documents/Master Science of Logistics/SPRING 2026/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="654" documentId="8_{06D03841-CD79-4205-A8AD-5C0B3B3C6826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7F5782E-20B7-449A-AB37-589BB16D516F}"/>
+  <xr:revisionPtr revIDLastSave="683" documentId="8_{06D03841-CD79-4205-A8AD-5C0B3B3C6826}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{12201831-ABB3-4D4A-BA76-A9FED9FA706D}"/>
   <bookViews>
     <workbookView xWindow="-28910" yWindow="2610" windowWidth="29020" windowHeight="15820" xr2:uid="{DEE70074-BDA1-42D2-9A3F-BB1A0D65DD0C}"/>
   </bookViews>
@@ -5280,37 +5280,37 @@
         <v>59</v>
       </c>
       <c r="B16" s="2">
-        <v>143.59573402608137</v>
+        <v>0</v>
       </c>
       <c r="C16" s="2">
-        <v>130.65833643185263</v>
+        <v>0</v>
       </c>
       <c r="D16" s="2">
-        <v>189.81796558916142</v>
+        <v>0</v>
       </c>
       <c r="E16" s="2">
-        <v>130.05686902280198</v>
+        <v>0</v>
       </c>
       <c r="F16" s="2">
-        <v>122.49963855600504</v>
+        <v>0</v>
       </c>
       <c r="G16" s="2">
-        <v>147.00711915853796</v>
+        <v>0</v>
       </c>
       <c r="H16" s="2">
-        <v>173.97568003476357</v>
+        <v>0</v>
       </c>
       <c r="I16" s="2">
-        <v>141.60200594271436</v>
+        <v>0</v>
       </c>
       <c r="J16" s="2">
-        <v>128.75756332364546</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2">
-        <v>133.50668393474322</v>
+        <v>0</v>
       </c>
       <c r="L16" s="2">
-        <v>177.97127153812642</v>
+        <v>0</v>
       </c>
       <c r="M16" s="2">
         <v>0</v>
@@ -5319,28 +5319,28 @@
         <v>0</v>
       </c>
       <c r="O16" s="2">
-        <v>158.32539191558445</v>
+        <v>0</v>
       </c>
       <c r="P16" s="2">
-        <v>158.81734963122844</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="2">
-        <v>134.11069487501771</v>
+        <v>0</v>
       </c>
       <c r="R16" s="2">
-        <v>153.32368110145771</v>
+        <v>0</v>
       </c>
       <c r="S16" s="2">
-        <v>171.90580594972559</v>
+        <v>0</v>
       </c>
       <c r="T16" s="2">
-        <v>137.58361631299604</v>
+        <v>0</v>
       </c>
       <c r="U16" s="2">
-        <v>159.88003792698896</v>
+        <v>0</v>
       </c>
       <c r="V16" s="2">
-        <v>150.53094078028644</v>
+        <v>0</v>
       </c>
       <c r="W16" s="2">
         <v>192.44538461538463</v>
@@ -6655,37 +6655,37 @@
         <v>64</v>
       </c>
       <c r="B21" s="2">
-        <v>111.25814259707963</v>
+        <v>0</v>
       </c>
       <c r="C21" s="2">
-        <v>78.000988528959027</v>
+        <v>0</v>
       </c>
       <c r="D21" s="2">
-        <v>79.680270691536023</v>
+        <v>0</v>
       </c>
       <c r="E21" s="2">
-        <v>105.01904349708981</v>
+        <v>0</v>
       </c>
       <c r="F21" s="2">
-        <v>105.72370441082521</v>
+        <v>0</v>
       </c>
       <c r="G21" s="2">
-        <v>111.04467306534816</v>
+        <v>0</v>
       </c>
       <c r="H21" s="2">
-        <v>94.761140763512529</v>
+        <v>0</v>
       </c>
       <c r="I21" s="2">
-        <v>100.80595990177549</v>
+        <v>0</v>
       </c>
       <c r="J21" s="2">
-        <v>95.421208586546186</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2">
-        <v>71.132646444247285</v>
+        <v>0</v>
       </c>
       <c r="L21" s="2">
-        <v>90.971395265740497</v>
+        <v>0</v>
       </c>
       <c r="M21" s="2">
         <v>0</v>
@@ -6694,16 +6694,16 @@
         <v>0</v>
       </c>
       <c r="O21" s="2">
-        <v>96.523050516552388</v>
+        <v>0</v>
       </c>
       <c r="P21" s="2">
-        <v>90.117474378868167</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="2">
-        <v>112.33537837807495</v>
+        <v>0</v>
       </c>
       <c r="R21" s="2">
-        <v>92.753544014273615</v>
+        <v>0</v>
       </c>
       <c r="S21" s="2">
         <v>31.324395604395619</v>
